--- a/blog/canada_overdoses/data_canada_overdoses.xlsx
+++ b/blog/canada_overdoses/data_canada_overdoses.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="BC Annual" sheetId="4" r:id="rId1"/>
@@ -425,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -448,6 +448,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -743,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1059,7 +1060,7 @@
         <v>2022</v>
       </c>
       <c r="B29">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="C29">
         <v>44.5</v>
@@ -1070,10 +1071,32 @@
         <v>2023</v>
       </c>
       <c r="B30">
-        <v>2574</v>
+        <v>2593</v>
       </c>
       <c r="C30">
-        <v>46.6</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>2024</v>
+      </c>
+      <c r="B31">
+        <v>2318</v>
+      </c>
+      <c r="C31">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>2025</v>
+      </c>
+      <c r="B32">
+        <v>1821</v>
+      </c>
+      <c r="C32">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2941,10 +2964,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>46</v>
       </c>
@@ -2990,8 +3013,11 @@
       <c r="O1">
         <v>2024</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -3023,22 +3049,25 @@
         <v>94</v>
       </c>
       <c r="K2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2">
         <v>188</v>
       </c>
       <c r="M2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O2">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>221</v>
+      </c>
+      <c r="P2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -3067,25 +3096,28 @@
         <v>108</v>
       </c>
       <c r="J3">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K3">
         <v>79</v>
       </c>
       <c r="L3">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M3">
         <v>203</v>
       </c>
       <c r="N3">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>204</v>
+      </c>
+      <c r="P3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -3108,13 +3140,13 @@
         <v>76</v>
       </c>
       <c r="H4">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I4">
         <v>158</v>
       </c>
       <c r="J4">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K4">
         <v>120</v>
@@ -3126,13 +3158,16 @@
         <v>185</v>
       </c>
       <c r="N4">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O4">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>219</v>
+      </c>
+      <c r="P4">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -3155,31 +3190,34 @@
         <v>73</v>
       </c>
       <c r="H5">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I5">
         <v>136</v>
       </c>
       <c r="J5">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K5">
         <v>130</v>
       </c>
       <c r="L5">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M5">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N5">
         <v>240</v>
       </c>
       <c r="O5">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>196</v>
+      </c>
+      <c r="P5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -3205,13 +3243,13 @@
         <v>149</v>
       </c>
       <c r="I6">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J6">
         <v>93</v>
       </c>
       <c r="K6">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L6">
         <v>174</v>
@@ -3220,13 +3258,16 @@
         <v>214</v>
       </c>
       <c r="N6">
+        <v>200</v>
+      </c>
+      <c r="O6">
         <v>198</v>
       </c>
-      <c r="O6">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -3249,31 +3290,34 @@
         <v>72</v>
       </c>
       <c r="H7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J7">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K7">
         <v>189</v>
       </c>
       <c r="L7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="N7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O7">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>201</v>
+      </c>
+      <c r="P7">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -3305,22 +3349,25 @@
         <v>72</v>
       </c>
       <c r="K8">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L8">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M8">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N8">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O8">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>194</v>
+      </c>
+      <c r="P8">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -3343,7 +3390,7 @@
         <v>65</v>
       </c>
       <c r="H9">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I9">
         <v>126</v>
@@ -3352,22 +3399,25 @@
         <v>83</v>
       </c>
       <c r="K9">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L9">
         <v>202</v>
       </c>
       <c r="M9">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N9">
         <v>199</v>
       </c>
       <c r="O9">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>210</v>
+      </c>
+      <c r="P9">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -3393,13 +3443,13 @@
         <v>97</v>
       </c>
       <c r="I10">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J10">
         <v>63</v>
       </c>
       <c r="K10">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L10">
         <v>161</v>
@@ -3411,10 +3461,13 @@
         <v>191</v>
       </c>
       <c r="O10">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>192</v>
+      </c>
+      <c r="P10">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -3440,25 +3493,31 @@
         <v>98</v>
       </c>
       <c r="I11">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J11">
         <v>79</v>
       </c>
       <c r="K11">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L11">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M11">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N11">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>217</v>
+      </c>
+      <c r="O11">
+        <v>163</v>
+      </c>
+      <c r="P11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -3481,28 +3540,34 @@
         <v>140</v>
       </c>
       <c r="H12">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I12">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J12">
         <v>81</v>
       </c>
       <c r="K12">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L12">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M12">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N12">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>231</v>
+      </c>
+      <c r="O12">
+        <v>157</v>
+      </c>
+      <c r="P12">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -3519,10 +3584,10 @@
         <v>25</v>
       </c>
       <c r="F13">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H13">
         <v>104</v>
@@ -3531,19 +3596,25 @@
         <v>127</v>
       </c>
       <c r="J13">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K13">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L13">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M13">
         <v>234</v>
       </c>
       <c r="N13">
-        <v>237</v>
+        <v>242</v>
+      </c>
+      <c r="O13">
+        <v>163</v>
+      </c>
+      <c r="P13">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -3553,7 +3624,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3619,7 +3690,7 @@
         <v>106</v>
       </c>
       <c r="C6">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3641,7 +3712,7 @@
         <v>272</v>
       </c>
       <c r="C8">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3649,10 +3720,10 @@
         <v>2018</v>
       </c>
       <c r="B9">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C9">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3660,10 +3731,10 @@
         <v>2019</v>
       </c>
       <c r="B10">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C10">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3671,7 +3742,7 @@
         <v>2020</v>
       </c>
       <c r="B11">
-        <v>235</v>
+        <v>333</v>
       </c>
       <c r="C11">
         <v>1441</v>
@@ -3693,10 +3764,10 @@
         <v>2022</v>
       </c>
       <c r="B13">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C13">
-        <v>1863</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3704,10 +3775,10 @@
         <v>2023</v>
       </c>
       <c r="B14">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C14">
-        <v>1995</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3715,10 +3786,21 @@
         <v>2024</v>
       </c>
       <c r="B15">
-        <v>491</v>
+        <v>579</v>
       </c>
       <c r="C15">
-        <v>1434</v>
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>2025</v>
+      </c>
+      <c r="B16">
+        <v>410</v>
+      </c>
+      <c r="C16">
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -3728,10 +3810,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>56</v>
       </c>
@@ -3774,8 +3856,14 @@
       <c r="N1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1">
+        <v>2024</v>
+      </c>
+      <c r="P1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -3801,25 +3889,31 @@
         <v>26</v>
       </c>
       <c r="I2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2">
         <v>13</v>
       </c>
       <c r="K2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>27</v>
+      </c>
+      <c r="O2">
+        <v>20</v>
+      </c>
+      <c r="P2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>54</v>
       </c>
@@ -3845,25 +3939,31 @@
         <v>271</v>
       </c>
       <c r="I3">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J3">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K3">
         <v>309</v>
       </c>
       <c r="L3">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="M3">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N3">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>345</v>
+      </c>
+      <c r="O3">
+        <v>307</v>
+      </c>
+      <c r="P3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -3880,19 +3980,19 @@
         <v>102</v>
       </c>
       <c r="F4">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G4">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H4">
         <v>400</v>
       </c>
       <c r="I4">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="J4">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K4">
         <v>413</v>
@@ -3901,13 +4001,19 @@
         <v>543</v>
       </c>
       <c r="M4">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="N4">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>646</v>
+      </c>
+      <c r="O4">
+        <v>570</v>
+      </c>
+      <c r="P4">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -3936,22 +4042,28 @@
         <v>346</v>
       </c>
       <c r="J5">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K5">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L5">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="M5">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="N5">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>576</v>
+      </c>
+      <c r="O5">
+        <v>586</v>
+      </c>
+      <c r="P5">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -3977,25 +4089,31 @@
         <v>315</v>
       </c>
       <c r="I6">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J6">
         <v>216</v>
       </c>
       <c r="K6">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="L6">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="M6">
         <v>575</v>
       </c>
       <c r="N6">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>587</v>
+      </c>
+      <c r="O6">
+        <v>478</v>
+      </c>
+      <c r="P6">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -4018,28 +4136,34 @@
         <v>50</v>
       </c>
       <c r="H7">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I7">
         <v>127</v>
       </c>
       <c r="J7">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K7">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L7">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N7">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>366</v>
+      </c>
+      <c r="O7">
+        <v>307</v>
+      </c>
+      <c r="P7">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -4074,13 +4198,19 @@
         <v>17</v>
       </c>
       <c r="L8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M8">
         <v>35</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="O8">
+        <v>49</v>
+      </c>
+      <c r="P8">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -4090,7 +4220,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -4269,7 +4399,7 @@
         <v>2021</v>
       </c>
       <c r="B13">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C13">
         <v>16</v>
@@ -4283,13 +4413,13 @@
         <v>2022</v>
       </c>
       <c r="B14">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C14">
         <v>25</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4297,13 +4427,41 @@
         <v>2023</v>
       </c>
       <c r="B15">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="C15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15">
         <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16">
+        <v>314</v>
+      </c>
+      <c r="C16">
+        <v>23</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>292</v>
+      </c>
+      <c r="C17">
+        <v>22</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4313,7 +4471,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4401,7 +4559,7 @@
         <v>2022</v>
       </c>
       <c r="B11">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4409,7 +4567,23 @@
         <v>2023</v>
       </c>
       <c r="B12">
-        <v>270</v>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>2024</v>
+      </c>
+      <c r="B13">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>2025</v>
+      </c>
+      <c r="B14">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -4419,14 +4593,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" s="21" t="s">
         <v>69</v>
       </c>
@@ -4475,8 +4649,14 @@
       <c r="P1" s="10">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="10">
+        <v>2024</v>
+      </c>
+      <c r="R1" s="10">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="4" t="s">
         <v>48</v>
       </c>
@@ -4525,8 +4705,14 @@
       <c r="P2" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="10">
+        <v>0</v>
+      </c>
+      <c r="R2" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
         <v>48</v>
       </c>
@@ -4575,8 +4761,14 @@
       <c r="P3" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" s="10">
+        <v>5</v>
+      </c>
+      <c r="R3" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="4" t="s">
         <v>48</v>
       </c>
@@ -4623,10 +4815,16 @@
         <v>18</v>
       </c>
       <c r="P4" s="10">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>20</v>
+      </c>
+      <c r="R4" s="10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
         <v>48</v>
       </c>
@@ -4673,10 +4871,16 @@
         <v>31</v>
       </c>
       <c r="P5" s="10">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>43</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>35</v>
+      </c>
+      <c r="R5" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="4" t="s">
         <v>48</v>
       </c>
@@ -4723,10 +4927,16 @@
         <v>24</v>
       </c>
       <c r="P6" s="10">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>29</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>27</v>
+      </c>
+      <c r="R6" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="4" t="s">
         <v>48</v>
       </c>
@@ -4773,10 +4983,16 @@
         <v>14</v>
       </c>
       <c r="P7" s="10">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>18</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>10</v>
+      </c>
+      <c r="R7" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="4" t="s">
         <v>48</v>
       </c>
@@ -4825,8 +5041,14 @@
       <c r="P8" s="10">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="10">
+        <v>8</v>
+      </c>
+      <c r="R8" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
@@ -4875,8 +5097,14 @@
       <c r="P9" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="10">
+        <v>0</v>
+      </c>
+      <c r="R9" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="7" t="s">
         <v>48</v>
       </c>
@@ -4925,8 +5153,14 @@
       <c r="P10" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
         <v>47</v>
       </c>
@@ -4975,8 +5209,14 @@
       <c r="P11" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="10">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="4" t="s">
         <v>47</v>
       </c>
@@ -5023,10 +5263,16 @@
         <v>3</v>
       </c>
       <c r="P12" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>2</v>
+      </c>
+      <c r="R12" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="4" t="s">
         <v>47</v>
       </c>
@@ -5073,10 +5319,16 @@
         <v>33</v>
       </c>
       <c r="P13" s="10">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>41</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>30</v>
+      </c>
+      <c r="R13" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="4" t="s">
         <v>47</v>
       </c>
@@ -5120,13 +5372,19 @@
         <v>46</v>
       </c>
       <c r="O14" s="13">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P14" s="10">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>69</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>50</v>
+      </c>
+      <c r="R14" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="4" t="s">
         <v>47</v>
       </c>
@@ -5173,10 +5431,16 @@
         <v>58</v>
       </c>
       <c r="P15" s="10">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+        <v>59</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>41</v>
+      </c>
+      <c r="R15" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="4" t="s">
         <v>47</v>
       </c>
@@ -5220,13 +5484,19 @@
         <v>47</v>
       </c>
       <c r="O16" s="13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P16" s="10">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+        <v>35</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>24</v>
+      </c>
+      <c r="R16" s="10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="4" t="s">
         <v>47</v>
       </c>
@@ -5275,8 +5545,14 @@
       <c r="P17" s="10">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17" s="10">
+        <v>8</v>
+      </c>
+      <c r="R17" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="4" t="s">
         <v>47</v>
       </c>
@@ -5325,8 +5601,14 @@
       <c r="P18" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18" s="10">
+        <v>1</v>
+      </c>
+      <c r="R18" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="7" t="s">
         <v>47</v>
       </c>
@@ -5373,6 +5655,12 @@
         <v>0</v>
       </c>
       <c r="P19" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>0</v>
+      </c>
+      <c r="R19" s="10">
         <v>0</v>
       </c>
     </row>
@@ -5383,14 +5671,14 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="21" t="s">
         <v>69</v>
       </c>
@@ -5433,15 +5721,20 @@
       <c r="N1" s="19">
         <v>2021</v>
       </c>
-      <c r="O1" s="18">
+      <c r="O1" s="22">
         <v>2022</v>
       </c>
-      <c r="P1" s="10">
+      <c r="P1" s="22">
         <v>2023</v>
       </c>
-      <c r="Q1" s="10"/>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="Q1" s="22">
+        <v>2024</v>
+      </c>
+      <c r="R1" s="18">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="4" t="s">
         <v>48</v>
       </c>
@@ -5484,14 +5777,20 @@
       <c r="N2" s="5">
         <v>25</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="10">
         <v>30</v>
       </c>
       <c r="P2" s="10">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="10">
+        <v>26</v>
+      </c>
+      <c r="R2" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
         <v>48</v>
       </c>
@@ -5534,14 +5833,20 @@
       <c r="N3" s="5">
         <v>71</v>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="10">
         <v>60</v>
       </c>
       <c r="P3" s="10">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+        <v>78</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>72</v>
+      </c>
+      <c r="R3" s="10">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="4" t="s">
         <v>48</v>
       </c>
@@ -5584,14 +5889,20 @@
       <c r="N4" s="5">
         <v>0</v>
       </c>
-      <c r="O4" s="13">
+      <c r="O4" s="10">
         <v>0</v>
       </c>
       <c r="P4" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="Q4" s="10">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
         <v>48</v>
       </c>
@@ -5634,14 +5945,20 @@
       <c r="N5" s="5">
         <v>0</v>
       </c>
-      <c r="O5" s="13">
+      <c r="O5" s="10">
         <v>0</v>
       </c>
       <c r="P5" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="Q5" s="10">
+        <v>0</v>
+      </c>
+      <c r="R5" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="4" t="s">
         <v>48</v>
       </c>
@@ -5684,14 +6001,20 @@
       <c r="N6" s="5">
         <v>0</v>
       </c>
-      <c r="O6" s="13">
+      <c r="O6" s="10">
         <v>0</v>
       </c>
       <c r="P6" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="Q6" s="10">
+        <v>0</v>
+      </c>
+      <c r="R6" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="4" t="s">
         <v>48</v>
       </c>
@@ -5734,14 +6057,20 @@
       <c r="N7" s="5">
         <v>3</v>
       </c>
-      <c r="O7" s="13">
+      <c r="O7" s="10">
         <v>3</v>
       </c>
       <c r="P7" s="10">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="Q7" s="10">
+        <v>1</v>
+      </c>
+      <c r="R7" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="4" t="s">
         <v>48</v>
       </c>
@@ -5784,14 +6113,20 @@
       <c r="N8" s="5">
         <v>0</v>
       </c>
-      <c r="O8" s="13">
+      <c r="O8" s="10">
         <v>1</v>
       </c>
       <c r="P8" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="Q8" s="10">
+        <v>1</v>
+      </c>
+      <c r="R8" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="7" t="s">
         <v>48</v>
       </c>
@@ -5834,14 +6169,20 @@
       <c r="N9" s="8">
         <v>8</v>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="10">
         <v>3</v>
       </c>
       <c r="P9" s="10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>5</v>
+      </c>
+      <c r="R9" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
         <v>47</v>
       </c>
@@ -5884,14 +6225,20 @@
       <c r="N10" s="2">
         <v>95</v>
       </c>
-      <c r="O10" s="16">
-        <v>75</v>
+      <c r="O10" s="10">
+        <v>76</v>
       </c>
       <c r="P10" s="10">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
+        <v>84</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>70</v>
+      </c>
+      <c r="R10" s="10">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="4" t="s">
         <v>47</v>
       </c>
@@ -5932,16 +6279,22 @@
         <v>78</v>
       </c>
       <c r="N11" s="5">
-        <v>92</v>
-      </c>
-      <c r="O11" s="13">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="O11" s="10">
+        <v>93</v>
       </c>
       <c r="P11" s="10">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
+        <v>112</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>66</v>
+      </c>
+      <c r="R11" s="10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="4" t="s">
         <v>47</v>
       </c>
@@ -5984,14 +6337,20 @@
       <c r="N12" s="5">
         <v>0</v>
       </c>
-      <c r="O12" s="13">
+      <c r="O12" s="10">
         <v>0</v>
       </c>
       <c r="P12" s="10">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="Q12" s="10">
+        <v>0</v>
+      </c>
+      <c r="R12" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="4" t="s">
         <v>47</v>
       </c>
@@ -6034,14 +6393,20 @@
       <c r="N13" s="5">
         <v>2</v>
       </c>
-      <c r="O13" s="13">
+      <c r="O13" s="10">
         <v>2</v>
       </c>
       <c r="P13" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="Q13" s="10">
+        <v>1</v>
+      </c>
+      <c r="R13" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="4" t="s">
         <v>47</v>
       </c>
@@ -6084,14 +6449,20 @@
       <c r="N14" s="5">
         <v>1</v>
       </c>
-      <c r="O14" s="13">
+      <c r="O14" s="10">
         <v>1</v>
       </c>
       <c r="P14" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="Q14" s="10">
+        <v>0</v>
+      </c>
+      <c r="R14" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="4" t="s">
         <v>47</v>
       </c>
@@ -6134,14 +6505,20 @@
       <c r="N15" s="5">
         <v>3</v>
       </c>
-      <c r="O15" s="13">
+      <c r="O15" s="10">
         <v>1</v>
       </c>
       <c r="P15" s="10">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="Q15" s="10">
+        <v>6</v>
+      </c>
+      <c r="R15" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="4" t="s">
         <v>47</v>
       </c>
@@ -6184,14 +6561,20 @@
       <c r="N16" s="5">
         <v>3</v>
       </c>
-      <c r="O16" s="13">
+      <c r="O16" s="10">
         <v>0</v>
       </c>
       <c r="P16" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16" s="10">
+        <v>0</v>
+      </c>
+      <c r="R16" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="7" t="s">
         <v>47</v>
       </c>
@@ -6234,11 +6617,17 @@
       <c r="N17" s="8">
         <v>12</v>
       </c>
-      <c r="O17" s="11">
+      <c r="O17" s="10">
         <v>11</v>
       </c>
       <c r="P17" s="10">
         <v>13</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>13</v>
+      </c>
+      <c r="R17" s="10">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -6266,1346 +6655,1346 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>2016</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>54</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>15.4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3">
+      <c r="A3" s="4">
         <v>2016</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="5">
         <v>47</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="6">
         <v>13.4</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4">
+      <c r="A4" s="4">
         <v>2016</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="5">
         <v>61</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="6">
         <v>17.399999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5">
+      <c r="A5" s="4">
         <v>2016</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="5">
         <v>49</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="6">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6">
+      <c r="A6" s="4">
         <v>2016</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="5">
         <v>59</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="6">
         <v>16.899999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7">
+      <c r="A7" s="4">
         <v>2016</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="5">
         <v>59</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="6">
         <v>16.899999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8">
+      <c r="A8" s="4">
         <v>2016</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="5">
         <v>69</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="6">
         <v>19.7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9">
+      <c r="A9" s="4">
         <v>2016</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="5">
         <v>48</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="6">
         <v>13.7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10">
+      <c r="A10" s="4">
         <v>2016</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="5">
         <v>56</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="6">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11">
+      <c r="A11" s="4">
         <v>2016</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="5">
         <v>53</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="6">
         <v>15.2</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12">
+      <c r="A12" s="4">
         <v>2016</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="5">
         <v>55</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="6">
         <v>15.7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13">
+      <c r="A13" s="7">
         <v>2016</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="8">
         <v>78</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="9">
         <v>22.3</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14">
+      <c r="A14" s="1">
         <v>2017</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>67</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="3">
         <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15">
+      <c r="A15" s="4">
         <v>2017</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="5">
         <v>56</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="6">
         <v>15.8</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16">
+      <c r="A16" s="4">
         <v>2017</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="5">
         <v>71</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="6">
         <v>20.100000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17">
+      <c r="A17" s="4">
         <v>2017</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="5">
         <v>71</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="6">
         <v>20.100000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18">
+      <c r="A18" s="4">
         <v>2017</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="5">
         <v>68</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="6">
         <v>19.2</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19">
+      <c r="A19" s="4">
         <v>2017</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="5">
         <v>61</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="6">
         <v>17.3</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20">
+      <c r="A20" s="4">
         <v>2017</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="5">
         <v>79</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="6">
         <v>22.4</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21">
+      <c r="A21" s="4">
         <v>2017</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="5">
         <v>63</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="6">
         <v>17.8</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22">
+      <c r="A22" s="4">
         <v>2017</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="5">
         <v>75</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="6">
         <v>21.2</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23">
+      <c r="A23" s="4">
         <v>2017</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="5">
         <v>66</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="6">
         <v>18.7</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24">
+      <c r="A24" s="4">
         <v>2017</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="5">
         <v>82</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="6">
         <v>23.2</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25">
+      <c r="A25" s="7">
         <v>2017</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="8">
         <v>103</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="9">
         <v>29.1</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26">
+      <c r="A26" s="1">
         <v>2018</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2">
         <v>77</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="3">
         <v>21.5</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27">
+      <c r="A27" s="4">
         <v>2018</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="5">
         <v>73</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="6">
         <v>20.399999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28">
+      <c r="A28" s="4">
         <v>2018</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="5">
         <v>77</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="6">
         <v>21.5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29">
+      <c r="A29" s="4">
         <v>2018</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="5">
         <v>76</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="6">
         <v>21.2</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30">
+      <c r="A30" s="4">
         <v>2018</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="5">
         <v>102</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="6">
         <v>28.5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31">
+      <c r="A31" s="4">
         <v>2018</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="5">
         <v>73</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="6">
         <v>20.399999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32">
+      <c r="A32" s="4">
         <v>2018</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="5">
         <v>80</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="6">
         <v>22.3</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33">
+      <c r="A33" s="4">
         <v>2018</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="5">
         <v>88</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="6">
         <v>24.6</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34">
+      <c r="A34" s="4">
         <v>2018</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="5">
         <v>73</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="6">
         <v>20.399999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35">
+      <c r="A35" s="4">
         <v>2018</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="5">
         <v>73</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="6">
         <v>20.399999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36">
+      <c r="A36" s="4">
         <v>2018</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="5">
         <v>74</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="6">
         <v>20.7</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37">
+      <c r="A37" s="7">
         <v>2018</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="8">
         <v>90</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="9">
         <v>25.1</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38">
+      <c r="A38" s="1">
         <v>2019</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="2">
         <v>73</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="3">
         <v>20.100000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39">
+      <c r="A39" s="4">
         <v>2019</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="5">
         <v>64</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="6">
         <v>17.600000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40">
+      <c r="A40" s="4">
         <v>2019</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="5">
         <v>67</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="6">
         <v>18.399999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41">
+      <c r="A41" s="4">
         <v>2019</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="5">
         <v>65</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="6">
         <v>17.899999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42">
+      <c r="A42" s="4">
         <v>2019</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="5">
         <v>75</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="6">
         <v>20.6</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43">
+      <c r="A43" s="4">
         <v>2019</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="5">
         <v>90</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="6">
         <v>24.8</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44">
+      <c r="A44" s="4">
         <v>2019</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="5">
         <v>83</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="6">
         <v>22.8</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45">
+      <c r="A45" s="4">
         <v>2019</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="5">
         <v>44</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="6">
         <v>12.1</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46">
+      <c r="A46" s="4">
         <v>2019</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="5">
         <v>72</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="6">
         <v>19.8</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47">
+      <c r="A47" s="4">
         <v>2019</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="5">
         <v>56</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="6">
         <v>15.4</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48">
+      <c r="A48" s="4">
         <v>2019</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="5">
         <v>61</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="6">
         <v>16.8</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49">
+      <c r="A49" s="7">
         <v>2019</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="8">
         <v>50</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="9">
         <v>13.8</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50">
+      <c r="A50" s="1">
         <v>2020</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="2">
         <v>68</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="3">
         <v>18.5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51">
+      <c r="A51" s="4">
         <v>2020</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="5">
         <v>57</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="6">
         <v>15.5</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52">
+      <c r="A52" s="4">
         <v>2020</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="5">
         <v>83</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="6">
         <v>22.6</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53">
+      <c r="A53" s="4">
         <v>2020</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="5">
         <v>101</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="6">
         <v>27.5</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54">
+      <c r="A54" s="4">
         <v>2020</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="5">
         <v>146</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="6">
         <v>39.799999999999997</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55">
+      <c r="A55" s="4">
         <v>2020</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="5">
         <v>142</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="6">
         <v>38.700000000000003</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56">
+      <c r="A56" s="4">
         <v>2020</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="5">
         <v>165</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="6">
         <v>44.9</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57">
+      <c r="A57" s="4">
         <v>2020</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="5">
         <v>125</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="6">
         <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58">
+      <c r="A58" s="4">
         <v>2020</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="5">
         <v>123</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="6">
         <v>33.5</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59">
+      <c r="A59" s="4">
         <v>2020</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="5">
         <v>119</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="6">
         <v>32.4</v>
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60">
+      <c r="A60" s="4">
         <v>2020</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="5">
         <v>133</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="6">
         <v>36.200000000000003</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61">
+      <c r="A61" s="7">
         <v>2020</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="8">
         <v>143</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="9">
         <v>38.9</v>
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62">
+      <c r="A62" s="1">
         <v>2021</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="2">
         <v>151</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="3">
         <v>40.9</v>
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63">
+      <c r="A63" s="4">
         <v>2021</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="5">
         <v>121</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="6">
         <v>32.799999999999997</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64">
+      <c r="A64" s="4">
         <v>2021</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="5">
         <v>142</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="6">
         <v>38.5</v>
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65">
+      <c r="A65" s="4">
         <v>2021</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="5">
         <v>141</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="6">
         <v>38.200000000000003</v>
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66">
+      <c r="A66" s="4">
         <v>2021</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="5">
         <v>148</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="6">
         <v>40.1</v>
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67">
+      <c r="A67" s="4">
         <v>2021</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="5">
         <v>152</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="6">
         <v>41.2</v>
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68">
+      <c r="A68" s="4">
         <v>2021</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="5">
         <v>148</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="6">
         <v>40.1</v>
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69">
+      <c r="A69" s="4">
         <v>2021</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="5">
         <v>149</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="6">
         <v>40.299999999999997</v>
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70">
+      <c r="A70" s="4">
         <v>2021</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="5">
         <v>176</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="6">
         <v>47.7</v>
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71">
+      <c r="A71" s="4">
         <v>2021</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="5">
         <v>176</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="6">
         <v>47.7</v>
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72">
+      <c r="A72" s="4">
         <v>2021</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="5">
         <v>192</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="6">
         <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73">
+      <c r="A73" s="7">
         <v>2021</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="8">
         <v>193</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="9">
         <v>52.3</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74">
+      <c r="A74" s="1">
         <v>2022</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="2">
         <v>179</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="3">
         <v>47.6</v>
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75">
+      <c r="A75" s="4">
         <v>2022</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="5">
         <v>188</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="6">
         <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76">
+      <c r="A76" s="4">
         <v>2022</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="5">
         <v>143</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="6">
         <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77">
+      <c r="A77" s="4">
         <v>2022</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="5">
         <v>139</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="6">
         <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78">
+      <c r="A78" s="4">
         <v>2022</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="5">
         <v>142</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="6">
         <v>37.799999999999997</v>
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79">
+      <c r="A79" s="4">
         <v>2022</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="5">
         <v>131</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="6">
         <v>34.9</v>
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80">
+      <c r="A80" s="4">
         <v>2022</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="5">
         <v>127</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="6">
         <v>33.799999999999997</v>
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81">
+      <c r="A81" s="4">
         <v>2022</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="5">
         <v>128</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="6">
         <v>34.1</v>
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82">
+      <c r="A82" s="4">
         <v>2022</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="5">
         <v>142</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="6">
         <v>37.799999999999997</v>
       </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83">
+      <c r="A83" s="4">
         <v>2022</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="5">
         <v>148</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="6">
         <v>39.4</v>
       </c>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84">
+      <c r="A84" s="4">
         <v>2022</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="5">
         <v>140</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="6">
         <v>37.200000000000003</v>
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85">
+      <c r="A85" s="7">
         <v>2022</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="8">
         <v>172</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="9">
         <v>45.8</v>
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86">
+      <c r="A86" s="1">
         <v>2023</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="2">
         <v>139</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="3">
         <v>35.6</v>
       </c>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87">
+      <c r="A87" s="4">
         <v>2023</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="5">
         <v>175</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="6">
         <v>44.8</v>
       </c>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88">
+      <c r="A88" s="4">
         <v>2023</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="5">
         <v>192</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="6">
         <v>49.2</v>
       </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89">
+      <c r="A89" s="4">
         <v>2023</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="5">
         <v>199</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="6">
         <v>51</v>
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90">
+      <c r="A90" s="4">
         <v>2023</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="5">
         <v>179</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="6">
         <v>45.9</v>
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91">
+      <c r="A91" s="4">
         <v>2023</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="5">
         <v>189</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="6">
         <v>48.4</v>
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92">
+      <c r="A92" s="4">
         <v>2023</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="5">
         <v>196</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="6">
         <v>50.2</v>
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93">
+      <c r="A93" s="4">
         <v>2023</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="5">
         <v>185</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="6">
         <v>47.4</v>
       </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94">
+      <c r="A94" s="4">
         <v>2023</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="5">
         <v>160</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="6">
         <v>41</v>
       </c>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95">
+      <c r="A95" s="4">
         <v>2023</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="5">
         <v>166</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="6">
         <v>42.5</v>
       </c>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96">
+      <c r="A96" s="4">
         <v>2023</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="5">
         <v>166</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="6">
         <v>42.5</v>
       </c>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97">
+      <c r="A97" s="7">
         <v>2023</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="8">
         <v>170</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="9">
         <v>43.5</v>
       </c>
     </row>
